--- a/simulation_summary_all_categories.xlsx
+++ b/simulation_summary_all_categories.xlsx
@@ -7,18 +7,380 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Light" sheetId="1" r:id="rId1"/>
-    <sheet name="Medium" sheetId="2" r:id="rId2"/>
-    <sheet name="Heavy" sheetId="3" r:id="rId3"/>
+    <sheet name="Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="Light" sheetId="2" r:id="rId2"/>
+    <sheet name="Medium" sheetId="3" r:id="rId3"/>
+    <sheet name="Heavy" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="116">
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Number_of_Households</t>
+  </si>
+  <si>
+    <t>Avg_Solar_Heating_Time_Pct</t>
+  </si>
+  <si>
+    <t>Avg_Grid_Heating_Time_Pct</t>
+  </si>
+  <si>
+    <t>Min_Solar_Heating_Time_Pct</t>
+  </si>
+  <si>
+    <t>Max_Solar_Heating_Time_Pct</t>
+  </si>
+  <si>
+    <t>Avg_Annual_Grid_kWh</t>
+  </si>
+  <si>
+    <t>Avg_Annual_Solar_kWh</t>
+  </si>
+  <si>
+    <t>Avg_Annual_Demand_kWh</t>
+  </si>
+  <si>
+    <t>Avg_Solar_Fraction</t>
+  </si>
+  <si>
+    <t>Avg_Annual_Cost_R</t>
+  </si>
+  <si>
+    <t>Avg_Cost_Without_Solar_R</t>
+  </si>
+  <si>
+    <t>Avg_Solar_Savings_R</t>
+  </si>
+  <si>
+    <t>Avg_Savings_Percentage</t>
+  </si>
+  <si>
+    <t>Min_Savings_Percentage</t>
+  </si>
+  <si>
+    <t>Max_Savings_Percentage</t>
+  </si>
+  <si>
+    <t>Total_Annual_Savings_R</t>
+  </si>
+  <si>
+    <t>Total_Grid_kWh</t>
+  </si>
+  <si>
+    <t>Total_Solar_kWh</t>
+  </si>
+  <si>
+    <t>Avg_Cold_Draw_Pct</t>
+  </si>
+  <si>
+    <t>Avg_Tank_Temp_C</t>
+  </si>
+  <si>
+    <t>Light</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Heavy</t>
+  </si>
+  <si>
+    <t>annual_grid_kwh</t>
+  </si>
+  <si>
+    <t>annual_solar_kwh</t>
+  </si>
+  <si>
+    <t>annual_demand_kwh</t>
+  </si>
+  <si>
+    <t>solar_fraction</t>
+  </si>
+  <si>
+    <t>cold_draw_pct</t>
+  </si>
+  <si>
+    <t>avg_temp</t>
+  </si>
+  <si>
+    <t>solar_used_when_needed_kwh</t>
+  </si>
+  <si>
+    <t>grid_used_when_needed_kwh</t>
+  </si>
+  <si>
+    <t>solar_heating_energy_fraction</t>
+  </si>
+  <si>
+    <t>solar_heating_event_fraction</t>
+  </si>
+  <si>
+    <t>annual_solar_savings_R</t>
+  </si>
+  <si>
+    <t>cost_without_solar_R</t>
+  </si>
+  <si>
+    <t>savings_percentage</t>
+  </si>
+  <si>
+    <t>solar_heating_time_percentage</t>
+  </si>
+  <si>
+    <t>grid_heating_time_percentage</t>
+  </si>
+  <si>
+    <t>cost_R</t>
+  </si>
+  <si>
+    <t>profile</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>light_01.csv</t>
+  </si>
+  <si>
+    <t>light_02.csv</t>
+  </si>
+  <si>
+    <t>light_03.csv</t>
+  </si>
+  <si>
+    <t>light_04.csv</t>
+  </si>
+  <si>
+    <t>light_05.csv</t>
+  </si>
+  <si>
+    <t>light_06.csv</t>
+  </si>
+  <si>
+    <t>light_07.csv</t>
+  </si>
+  <si>
+    <t>light_08.csv</t>
+  </si>
+  <si>
+    <t>light_09.csv</t>
+  </si>
+  <si>
+    <t>light_10.csv</t>
+  </si>
+  <si>
+    <t>light_11.csv</t>
+  </si>
+  <si>
+    <t>light_12.csv</t>
+  </si>
+  <si>
+    <t>light_13.csv</t>
+  </si>
+  <si>
+    <t>light_14.csv</t>
+  </si>
+  <si>
+    <t>light_15.csv</t>
+  </si>
+  <si>
+    <t>light_16.csv</t>
+  </si>
+  <si>
+    <t>light_17.csv</t>
+  </si>
+  <si>
+    <t>light_18.csv</t>
+  </si>
+  <si>
+    <t>light_19.csv</t>
+  </si>
+  <si>
+    <t>light_20.csv</t>
+  </si>
+  <si>
+    <t>light_21.csv</t>
+  </si>
+  <si>
+    <t>light_22.csv</t>
+  </si>
+  <si>
+    <t>light_23.csv</t>
+  </si>
+  <si>
+    <t>light_24.csv</t>
+  </si>
+  <si>
+    <t>light_25.csv</t>
+  </si>
+  <si>
+    <t>medium_01.csv</t>
+  </si>
+  <si>
+    <t>medium_02.csv</t>
+  </si>
+  <si>
+    <t>medium_03.csv</t>
+  </si>
+  <si>
+    <t>medium_04.csv</t>
+  </si>
+  <si>
+    <t>medium_05.csv</t>
+  </si>
+  <si>
+    <t>medium_06.csv</t>
+  </si>
+  <si>
+    <t>medium_07.csv</t>
+  </si>
+  <si>
+    <t>medium_08.csv</t>
+  </si>
+  <si>
+    <t>medium_09.csv</t>
+  </si>
+  <si>
+    <t>medium_10.csv</t>
+  </si>
+  <si>
+    <t>medium_11.csv</t>
+  </si>
+  <si>
+    <t>medium_12.csv</t>
+  </si>
+  <si>
+    <t>medium_13.csv</t>
+  </si>
+  <si>
+    <t>medium_14.csv</t>
+  </si>
+  <si>
+    <t>medium_15.csv</t>
+  </si>
+  <si>
+    <t>medium_16.csv</t>
+  </si>
+  <si>
+    <t>medium_17.csv</t>
+  </si>
+  <si>
+    <t>medium_18.csv</t>
+  </si>
+  <si>
+    <t>medium_19.csv</t>
+  </si>
+  <si>
+    <t>medium_20.csv</t>
+  </si>
+  <si>
+    <t>medium_21.csv</t>
+  </si>
+  <si>
+    <t>medium_22.csv</t>
+  </si>
+  <si>
+    <t>medium_23.csv</t>
+  </si>
+  <si>
+    <t>medium_24.csv</t>
+  </si>
+  <si>
+    <t>heavy_01.csv</t>
+  </si>
+  <si>
+    <t>heavy_02.csv</t>
+  </si>
+  <si>
+    <t>heavy_03.csv</t>
+  </si>
+  <si>
+    <t>heavy_04.csv</t>
+  </si>
+  <si>
+    <t>heavy_05.csv</t>
+  </si>
+  <si>
+    <t>heavy_06.csv</t>
+  </si>
+  <si>
+    <t>heavy_07.csv</t>
+  </si>
+  <si>
+    <t>heavy_08.csv</t>
+  </si>
+  <si>
+    <t>heavy_09.csv</t>
+  </si>
+  <si>
+    <t>heavy_10.csv</t>
+  </si>
+  <si>
+    <t>heavy_11.csv</t>
+  </si>
+  <si>
+    <t>heavy_12.csv</t>
+  </si>
+  <si>
+    <t>heavy_13.csv</t>
+  </si>
+  <si>
+    <t>heavy_14.csv</t>
+  </si>
+  <si>
+    <t>heavy_15.csv</t>
+  </si>
+  <si>
+    <t>heavy_16.csv</t>
+  </si>
+  <si>
+    <t>heavy_17.csv</t>
+  </si>
+  <si>
+    <t>heavy_18.csv</t>
+  </si>
+  <si>
+    <t>heavy_19.csv</t>
+  </si>
+  <si>
+    <t>heavy_20.csv</t>
+  </si>
+  <si>
+    <t>heavy_21.csv</t>
+  </si>
+  <si>
+    <t>heavy_22.csv</t>
+  </si>
+  <si>
+    <t>heavy_23.csv</t>
+  </si>
+  <si>
+    <t>heavy_24.csv</t>
+  </si>
+  <si>
+    <t>heavy_25.csv</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -34,7 +396,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +404,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -342,27 +722,4612 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:21">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2">
+        <v>25</v>
+      </c>
+      <c r="C2">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="D2">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="E2">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="F2">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="G2">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="H2">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="I2">
+        <v>50.50332066666666</v>
+      </c>
+      <c r="J2">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="K2">
+        <v>3998.6522112872</v>
+      </c>
+      <c r="L2">
+        <v>4052.4</v>
+      </c>
+      <c r="M2">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="N2">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="O2">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="P2">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="Q2">
+        <v>1343.694717820011</v>
+      </c>
+      <c r="R2">
+        <v>62274.47621733129</v>
+      </c>
+      <c r="S2">
+        <v>725.5237826687165</v>
+      </c>
+      <c r="T2">
+        <v>0.002380952380952381</v>
+      </c>
+      <c r="U2">
+        <v>89.80612932150416</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3">
+        <v>24</v>
+      </c>
+      <c r="C3">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="D3">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="E3">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="F3">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="G3">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="H3">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="I3">
+        <v>130.5556183333333</v>
+      </c>
+      <c r="J3">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="K3">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="L3">
+        <v>4052.4</v>
+      </c>
+      <c r="M3">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="N3">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="O3">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="P3">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="Q3">
+        <v>1289.94692910721</v>
+      </c>
+      <c r="R3">
+        <v>59783.49716863804</v>
+      </c>
+      <c r="S3">
+        <v>696.5028313619679</v>
+      </c>
+      <c r="T3">
+        <v>0.01240079365079365</v>
+      </c>
+      <c r="U3">
+        <v>89.47194523404471</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4">
+        <v>25</v>
+      </c>
+      <c r="C4">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="D4">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="E4">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="F4">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="G4">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="H4">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="I4">
+        <v>273.5699683333333</v>
+      </c>
+      <c r="J4">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="K4">
+        <v>3998.6522112872</v>
+      </c>
+      <c r="L4">
+        <v>4052.4</v>
+      </c>
+      <c r="M4">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="N4">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="O4">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="P4">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="Q4">
+        <v>1343.694717820011</v>
+      </c>
+      <c r="R4">
+        <v>62274.47621733129</v>
+      </c>
+      <c r="S4">
+        <v>725.5237826687165</v>
+      </c>
+      <c r="T4">
+        <v>0.2476190476190476</v>
+      </c>
+      <c r="U4">
+        <v>87.60345550060065</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:18">
+      <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B2">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C2">
+        <v>6.6944</v>
+      </c>
+      <c r="D2">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>89.94437053237519</v>
+      </c>
+      <c r="G2">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H2">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I2">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J2">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K2">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L2">
+        <v>4052.4</v>
+      </c>
+      <c r="M2">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N2">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O2">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P2">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B3">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C3">
+        <v>12.53456666666667</v>
+      </c>
+      <c r="D3">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>89.92565574937247</v>
+      </c>
+      <c r="G3">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H3">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I3">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J3">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K3">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L3">
+        <v>4052.4</v>
+      </c>
+      <c r="M3">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N3">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O3">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P3">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>43</v>
+      </c>
+      <c r="R3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B4">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C4">
+        <v>17.782</v>
+      </c>
+      <c r="D4">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>89.89917994744891</v>
+      </c>
+      <c r="G4">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H4">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I4">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J4">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K4">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L4">
+        <v>4052.4</v>
+      </c>
+      <c r="M4">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N4">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O4">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P4">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>44</v>
+      </c>
+      <c r="R4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B5">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C5">
+        <v>20.0832</v>
+      </c>
+      <c r="D5">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>89.94147389802825</v>
+      </c>
+      <c r="G5">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H5">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I5">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J5">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K5">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L5">
+        <v>4052.4</v>
+      </c>
+      <c r="M5">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N5">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O5">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P5">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>45</v>
+      </c>
+      <c r="R5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B6">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C6">
+        <v>29.88945</v>
+      </c>
+      <c r="D6">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>89.92227039329848</v>
+      </c>
+      <c r="G6">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H6">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I6">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J6">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K6">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L6">
+        <v>4052.4</v>
+      </c>
+      <c r="M6">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N6">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O6">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P6">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>46</v>
+      </c>
+      <c r="R6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B7">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C7">
+        <v>33.249725</v>
+      </c>
+      <c r="D7">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>89.93241224653057</v>
+      </c>
+      <c r="G7">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H7">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I7">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J7">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K7">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L7">
+        <v>4052.4</v>
+      </c>
+      <c r="M7">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N7">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O7">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P7">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B8">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C8">
+        <v>41.29956666666667</v>
+      </c>
+      <c r="D8">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>89.80543040662504</v>
+      </c>
+      <c r="G8">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H8">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I8">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J8">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K8">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L8">
+        <v>4052.4</v>
+      </c>
+      <c r="M8">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N8">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O8">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P8">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>48</v>
+      </c>
+      <c r="R8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B9">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C9">
+        <v>40.885525</v>
+      </c>
+      <c r="D9">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>89.84380716016692</v>
+      </c>
+      <c r="G9">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H9">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I9">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J9">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K9">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L9">
+        <v>4052.4</v>
+      </c>
+      <c r="M9">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N9">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O9">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P9">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>49</v>
+      </c>
+      <c r="R9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B10">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C10">
+        <v>43.74895000000001</v>
+      </c>
+      <c r="D10">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>89.85852721190152</v>
+      </c>
+      <c r="G10">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H10">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I10">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J10">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K10">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L10">
+        <v>4052.4</v>
+      </c>
+      <c r="M10">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N10">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O10">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P10">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>50</v>
+      </c>
+      <c r="R10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B11">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C11">
+        <v>42.05791666666666</v>
+      </c>
+      <c r="D11">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>89.88056917209485</v>
+      </c>
+      <c r="G11">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H11">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I11">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J11">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K11">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L11">
+        <v>4052.4</v>
+      </c>
+      <c r="M11">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N11">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O11">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P11">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>51</v>
+      </c>
+      <c r="R11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B12">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C12">
+        <v>41.98818333333333</v>
+      </c>
+      <c r="D12">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>89.8878809888203</v>
+      </c>
+      <c r="G12">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H12">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I12">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J12">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K12">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L12">
+        <v>4052.4</v>
+      </c>
+      <c r="M12">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N12">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O12">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P12">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>52</v>
+      </c>
+      <c r="R12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B13">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C13">
+        <v>43.01675</v>
+      </c>
+      <c r="D13">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>89.85708615563847</v>
+      </c>
+      <c r="G13">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H13">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I13">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J13">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K13">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L13">
+        <v>4052.4</v>
+      </c>
+      <c r="M13">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N13">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O13">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P13">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>53</v>
+      </c>
+      <c r="R13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B14">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C14">
+        <v>52.25205833333333</v>
+      </c>
+      <c r="D14">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>89.89459109959775</v>
+      </c>
+      <c r="G14">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H14">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I14">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J14">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K14">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L14">
+        <v>4052.4</v>
+      </c>
+      <c r="M14">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N14">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O14">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P14">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>54</v>
+      </c>
+      <c r="R14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B15">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C15">
+        <v>51.397825</v>
+      </c>
+      <c r="D15">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>89.85520699800848</v>
+      </c>
+      <c r="G15">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H15">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I15">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J15">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K15">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L15">
+        <v>4052.4</v>
+      </c>
+      <c r="M15">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N15">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O15">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P15">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>55</v>
+      </c>
+      <c r="R15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B16">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C16">
+        <v>58.2099</v>
+      </c>
+      <c r="D16">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>89.86220513509667</v>
+      </c>
+      <c r="G16">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H16">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I16">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J16">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K16">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L16">
+        <v>4052.4</v>
+      </c>
+      <c r="M16">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N16">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O16">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P16">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>56</v>
+      </c>
+      <c r="R16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B17">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C17">
+        <v>65.38371666666667</v>
+      </c>
+      <c r="D17">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>89.88168843066468</v>
+      </c>
+      <c r="G17">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H17">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I17">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J17">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K17">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L17">
+        <v>4052.4</v>
+      </c>
+      <c r="M17">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N17">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O17">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P17">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>57</v>
+      </c>
+      <c r="R17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B18">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C18">
+        <v>65.16579999999999</v>
+      </c>
+      <c r="D18">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>89.85490921642764</v>
+      </c>
+      <c r="G18">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H18">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I18">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J18">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K18">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L18">
+        <v>4052.4</v>
+      </c>
+      <c r="M18">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N18">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O18">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P18">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>58</v>
+      </c>
+      <c r="R18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="A19">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B19">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C19">
+        <v>70.59192499999999</v>
+      </c>
+      <c r="D19">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>89.64910178807773</v>
+      </c>
+      <c r="G19">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H19">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I19">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J19">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K19">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L19">
+        <v>4052.4</v>
+      </c>
+      <c r="M19">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N19">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O19">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P19">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>59</v>
+      </c>
+      <c r="R19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="A20">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B20">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C20">
+        <v>68.57401666666667</v>
+      </c>
+      <c r="D20">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>89.83562110324218</v>
+      </c>
+      <c r="G20">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H20">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I20">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J20">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K20">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L20">
+        <v>4052.4</v>
+      </c>
+      <c r="M20">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N20">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O20">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P20">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>60</v>
+      </c>
+      <c r="R20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B21">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C21">
+        <v>73.45535000000001</v>
+      </c>
+      <c r="D21">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>89.79395239579016</v>
+      </c>
+      <c r="G21">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H21">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I21">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J21">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K21">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L21">
+        <v>4052.4</v>
+      </c>
+      <c r="M21">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N21">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O21">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P21">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>61</v>
+      </c>
+      <c r="R21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B22">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C22">
+        <v>77.28196666666666</v>
+      </c>
+      <c r="D22">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>89.19253122769216</v>
+      </c>
+      <c r="G22">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H22">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I22">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J22">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K22">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L22">
+        <v>4052.4</v>
+      </c>
+      <c r="M22">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N22">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O22">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P22">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>62</v>
+      </c>
+      <c r="R22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B23">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C23">
+        <v>77.22094999999999</v>
+      </c>
+      <c r="D23">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>89.72150882996829</v>
+      </c>
+      <c r="G23">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H23">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I23">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J23">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K23">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L23">
+        <v>4052.4</v>
+      </c>
+      <c r="M23">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N23">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O23">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P23">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>63</v>
+      </c>
+      <c r="R23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="A24">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B24">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C24">
+        <v>77.8747</v>
+      </c>
+      <c r="D24">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>89.80627642270433</v>
+      </c>
+      <c r="G24">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H24">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I24">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J24">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K24">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L24">
+        <v>4052.4</v>
+      </c>
+      <c r="M24">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N24">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O24">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P24">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>64</v>
+      </c>
+      <c r="R24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="A25">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B25">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C25">
+        <v>76.881</v>
+      </c>
+      <c r="D25">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E25">
+        <v>0.05952380952380953</v>
+      </c>
+      <c r="F25">
+        <v>89.51210981756179</v>
+      </c>
+      <c r="G25">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H25">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I25">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J25">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K25">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L25">
+        <v>4052.4</v>
+      </c>
+      <c r="M25">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N25">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O25">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P25">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>65</v>
+      </c>
+      <c r="R25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="A26">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B26">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C26">
+        <v>75.063575</v>
+      </c>
+      <c r="D26">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>89.59486671047105</v>
+      </c>
+      <c r="G26">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H26">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I26">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J26">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K26">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L26">
+        <v>4052.4</v>
+      </c>
+      <c r="M26">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N26">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O26">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P26">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>66</v>
+      </c>
+      <c r="R26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:18">
+      <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B2">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C2">
+        <v>84.38605</v>
+      </c>
+      <c r="D2">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>89.71592665158781</v>
+      </c>
+      <c r="G2">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H2">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I2">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J2">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K2">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L2">
+        <v>4052.4</v>
+      </c>
+      <c r="M2">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N2">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O2">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P2">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>67</v>
+      </c>
+      <c r="R2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B3">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C3">
+        <v>87.71145833333333</v>
+      </c>
+      <c r="D3">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>89.87923387878239</v>
+      </c>
+      <c r="G3">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H3">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I3">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J3">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K3">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L3">
+        <v>4052.4</v>
+      </c>
+      <c r="M3">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N3">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O3">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P3">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>68</v>
+      </c>
+      <c r="R3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B4">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C4">
+        <v>87.34099999999999</v>
+      </c>
+      <c r="D4">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>89.63716425420411</v>
+      </c>
+      <c r="G4">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H4">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I4">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J4">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K4">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L4">
+        <v>4052.4</v>
+      </c>
+      <c r="M4">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N4">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O4">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P4">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>69</v>
+      </c>
+      <c r="R4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B5">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C5">
+        <v>98.79905833333333</v>
+      </c>
+      <c r="D5">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>89.75183136017601</v>
+      </c>
+      <c r="G5">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H5">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I5">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J5">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K5">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L5">
+        <v>4052.4</v>
+      </c>
+      <c r="M5">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N5">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O5">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P5">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B6">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C6">
+        <v>100.3637</v>
+      </c>
+      <c r="D6">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>89.54521225051407</v>
+      </c>
+      <c r="G6">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H6">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I6">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J6">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K6">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L6">
+        <v>4052.4</v>
+      </c>
+      <c r="M6">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N6">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O6">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P6">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>71</v>
+      </c>
+      <c r="R6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B7">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C7">
+        <v>104.5171916666667</v>
+      </c>
+      <c r="D7">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>89.62401019090751</v>
+      </c>
+      <c r="G7">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H7">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I7">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J7">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K7">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L7">
+        <v>4052.4</v>
+      </c>
+      <c r="M7">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N7">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O7">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P7">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>72</v>
+      </c>
+      <c r="R7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B8">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C8">
+        <v>109.8343583333333</v>
+      </c>
+      <c r="D8">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>89.71859098677129</v>
+      </c>
+      <c r="G8">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H8">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I8">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J8">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K8">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L8">
+        <v>4052.4</v>
+      </c>
+      <c r="M8">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N8">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O8">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P8">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>73</v>
+      </c>
+      <c r="R8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B9">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C9">
+        <v>108.5556233333333</v>
+      </c>
+      <c r="D9">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>89.66557715604016</v>
+      </c>
+      <c r="G9">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H9">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I9">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J9">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K9">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L9">
+        <v>4052.4</v>
+      </c>
+      <c r="M9">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N9">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O9">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P9">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>74</v>
+      </c>
+      <c r="R9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B10">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C10">
+        <v>113.3166666666667</v>
+      </c>
+      <c r="D10">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>89.80391085487025</v>
+      </c>
+      <c r="G10">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H10">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I10">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J10">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K10">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L10">
+        <v>4052.4</v>
+      </c>
+      <c r="M10">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N10">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O10">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P10">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>75</v>
+      </c>
+      <c r="R10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B11">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C11">
+        <v>123.3321166666667</v>
+      </c>
+      <c r="D11">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>89.56897049709033</v>
+      </c>
+      <c r="G11">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H11">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I11">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J11">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K11">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L11">
+        <v>4052.4</v>
+      </c>
+      <c r="M11">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N11">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O11">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P11">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>76</v>
+      </c>
+      <c r="R11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B12">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C12">
+        <v>116.8556333333333</v>
+      </c>
+      <c r="D12">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>89.78728758465104</v>
+      </c>
+      <c r="G12">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H12">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I12">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J12">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K12">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L12">
+        <v>4052.4</v>
+      </c>
+      <c r="M12">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N12">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O12">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P12">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>77</v>
+      </c>
+      <c r="R12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B13">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C13">
+        <v>120.9088833333333</v>
+      </c>
+      <c r="D13">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>89.83020869706915</v>
+      </c>
+      <c r="G13">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H13">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I13">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J13">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K13">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L13">
+        <v>4052.4</v>
+      </c>
+      <c r="M13">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N13">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O13">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P13">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>78</v>
+      </c>
+      <c r="R13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B14">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C14">
+        <v>124.9447</v>
+      </c>
+      <c r="D14">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>88.90023759121726</v>
+      </c>
+      <c r="G14">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H14">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I14">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J14">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K14">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L14">
+        <v>4052.4</v>
+      </c>
+      <c r="M14">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N14">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O14">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P14">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>79</v>
+      </c>
+      <c r="R14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B15">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C15">
+        <v>134.3674166666667</v>
+      </c>
+      <c r="D15">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>89.55753025435205</v>
+      </c>
+      <c r="G15">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H15">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I15">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J15">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K15">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L15">
+        <v>4052.4</v>
+      </c>
+      <c r="M15">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N15">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O15">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P15">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>80</v>
+      </c>
+      <c r="R15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B16">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C16">
+        <v>137.78435</v>
+      </c>
+      <c r="D16">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>89.72220539967149</v>
+      </c>
+      <c r="G16">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H16">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I16">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J16">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K16">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L16">
+        <v>4052.4</v>
+      </c>
+      <c r="M16">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N16">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O16">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P16">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>81</v>
+      </c>
+      <c r="R16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B17">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C17">
+        <v>149.3993083333333</v>
+      </c>
+      <c r="D17">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>89.6314015623996</v>
+      </c>
+      <c r="G17">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H17">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I17">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J17">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K17">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L17">
+        <v>4052.4</v>
+      </c>
+      <c r="M17">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N17">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O17">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P17">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>82</v>
+      </c>
+      <c r="R17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B18">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C18">
+        <v>136.803725</v>
+      </c>
+      <c r="D18">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>89.13521009936646</v>
+      </c>
+      <c r="G18">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H18">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I18">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J18">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K18">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L18">
+        <v>4052.4</v>
+      </c>
+      <c r="M18">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N18">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O18">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P18">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>83</v>
+      </c>
+      <c r="R18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="A19">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B19">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C19">
+        <v>169.4171333333333</v>
+      </c>
+      <c r="D19">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>89.34153613548463</v>
+      </c>
+      <c r="G19">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H19">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I19">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J19">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K19">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L19">
+        <v>4052.4</v>
+      </c>
+      <c r="M19">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N19">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O19">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P19">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>84</v>
+      </c>
+      <c r="R19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="A20">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B20">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C20">
+        <v>159.4539833333334</v>
+      </c>
+      <c r="D20">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>89.37834313270919</v>
+      </c>
+      <c r="G20">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H20">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I20">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J20">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K20">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L20">
+        <v>4052.4</v>
+      </c>
+      <c r="M20">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N20">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O20">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P20">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>85</v>
+      </c>
+      <c r="R20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B21">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C21">
+        <v>166.7411166666667</v>
+      </c>
+      <c r="D21">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>88.36909523071991</v>
+      </c>
+      <c r="G21">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H21">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I21">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J21">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K21">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L21">
+        <v>4052.4</v>
+      </c>
+      <c r="M21">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N21">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O21">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P21">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>86</v>
+      </c>
+      <c r="R21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B22">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C22">
+        <v>173.1740166666667</v>
+      </c>
+      <c r="D22">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>89.56171816751764</v>
+      </c>
+      <c r="G22">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H22">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I22">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J22">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K22">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L22">
+        <v>4052.4</v>
+      </c>
+      <c r="M22">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N22">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O22">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P22">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>87</v>
+      </c>
+      <c r="R22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B23">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C23">
+        <v>180.1952916666667</v>
+      </c>
+      <c r="D23">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>89.44935803598639</v>
+      </c>
+      <c r="G23">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H23">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I23">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J23">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K23">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L23">
+        <v>4052.4</v>
+      </c>
+      <c r="M23">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N23">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O23">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P23">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>88</v>
+      </c>
+      <c r="R23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="A24">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B24">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C24">
+        <v>173.3265583333333</v>
+      </c>
+      <c r="D24">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>89.04151204838408</v>
+      </c>
+      <c r="G24">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H24">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I24">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J24">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K24">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L24">
+        <v>4052.4</v>
+      </c>
+      <c r="M24">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N24">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O24">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P24">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>89</v>
+      </c>
+      <c r="R24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="A25">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B25">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C25">
+        <v>171.8055</v>
+      </c>
+      <c r="D25">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E25">
+        <v>0.2976190476190476</v>
+      </c>
+      <c r="F25">
+        <v>88.7106135966001</v>
+      </c>
+      <c r="G25">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H25">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I25">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J25">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K25">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L25">
+        <v>4052.4</v>
+      </c>
+      <c r="M25">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N25">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O25">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P25">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>90</v>
+      </c>
+      <c r="R25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:R26"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:18">
+      <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B2">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C2">
+        <v>185.834975</v>
+      </c>
+      <c r="D2">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>89.49749983602398</v>
+      </c>
+      <c r="G2">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H2">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I2">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J2">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K2">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L2">
+        <v>4052.4</v>
+      </c>
+      <c r="M2">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N2">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O2">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P2">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>91</v>
+      </c>
+      <c r="R2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B3">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C3">
+        <v>188.2756416666666</v>
+      </c>
+      <c r="D3">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>89.24530257843237</v>
+      </c>
+      <c r="G3">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H3">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I3">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J3">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K3">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L3">
+        <v>4052.4</v>
+      </c>
+      <c r="M3">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N3">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O3">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P3">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>92</v>
+      </c>
+      <c r="R3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B4">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C4">
+        <v>202.6537833333333</v>
+      </c>
+      <c r="D4">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>88.58636959873658</v>
+      </c>
+      <c r="G4">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H4">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I4">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J4">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K4">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L4">
+        <v>4052.4</v>
+      </c>
+      <c r="M4">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N4">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O4">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P4">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>93</v>
+      </c>
+      <c r="R4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B5">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C5">
+        <v>208.1714333333333</v>
+      </c>
+      <c r="D5">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>89.00373958616397</v>
+      </c>
+      <c r="G5">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H5">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I5">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J5">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K5">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L5">
+        <v>4052.4</v>
+      </c>
+      <c r="M5">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N5">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O5">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P5">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>94</v>
+      </c>
+      <c r="R5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B6">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C6">
+        <v>215.9902833333333</v>
+      </c>
+      <c r="D6">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E6">
+        <v>0.2281746031746032</v>
+      </c>
+      <c r="F6">
+        <v>88.17673083707085</v>
+      </c>
+      <c r="G6">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H6">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I6">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J6">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K6">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L6">
+        <v>4052.4</v>
+      </c>
+      <c r="M6">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N6">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O6">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P6">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>95</v>
+      </c>
+      <c r="R6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B7">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C7">
+        <v>212.8784333333333</v>
+      </c>
+      <c r="D7">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>88.82025439897599</v>
+      </c>
+      <c r="G7">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H7">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I7">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J7">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K7">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L7">
+        <v>4052.4</v>
+      </c>
+      <c r="M7">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N7">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O7">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P7">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>96</v>
+      </c>
+      <c r="R7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B8">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C8">
+        <v>227.68805</v>
+      </c>
+      <c r="D8">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>88.2741947568348</v>
+      </c>
+      <c r="G8">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H8">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I8">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J8">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K8">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L8">
+        <v>4052.4</v>
+      </c>
+      <c r="M8">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N8">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O8">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P8">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>97</v>
+      </c>
+      <c r="R8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B9">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C9">
+        <v>237.83425</v>
+      </c>
+      <c r="D9">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E9">
+        <v>0.00992063492063492</v>
+      </c>
+      <c r="F9">
+        <v>87.64123351064343</v>
+      </c>
+      <c r="G9">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H9">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I9">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J9">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K9">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L9">
+        <v>4052.4</v>
+      </c>
+      <c r="M9">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N9">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O9">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P9">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>98</v>
+      </c>
+      <c r="R9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B10">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C10">
+        <v>244.5548</v>
+      </c>
+      <c r="D10">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E10">
+        <v>0.08928571428571429</v>
+      </c>
+      <c r="F10">
+        <v>87.41212236357964</v>
+      </c>
+      <c r="G10">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H10">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I10">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J10">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K10">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L10">
+        <v>4052.4</v>
+      </c>
+      <c r="M10">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N10">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O10">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P10">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>99</v>
+      </c>
+      <c r="R10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B11">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C11">
+        <v>249.5080458333333</v>
+      </c>
+      <c r="D11">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>88.62652343466712</v>
+      </c>
+      <c r="G11">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H11">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I11">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J11">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K11">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L11">
+        <v>4052.4</v>
+      </c>
+      <c r="M11">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N11">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O11">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P11">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>100</v>
+      </c>
+      <c r="R11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B12">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C12">
+        <v>255.98235</v>
+      </c>
+      <c r="D12">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>89.0974183576907</v>
+      </c>
+      <c r="G12">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H12">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I12">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J12">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K12">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L12">
+        <v>4052.4</v>
+      </c>
+      <c r="M12">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N12">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O12">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P12">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>101</v>
+      </c>
+      <c r="R12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B13">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C13">
+        <v>249.0526</v>
+      </c>
+      <c r="D13">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>87.03839846862981</v>
+      </c>
+      <c r="G13">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H13">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I13">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J13">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K13">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L13">
+        <v>4052.4</v>
+      </c>
+      <c r="M13">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N13">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O13">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P13">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>102</v>
+      </c>
+      <c r="R13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B14">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C14">
+        <v>279.608875</v>
+      </c>
+      <c r="D14">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E14">
+        <v>0.3273809523809524</v>
+      </c>
+      <c r="F14">
+        <v>87.65025319531638</v>
+      </c>
+      <c r="G14">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H14">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I14">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J14">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K14">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L14">
+        <v>4052.4</v>
+      </c>
+      <c r="M14">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N14">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O14">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P14">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>103</v>
+      </c>
+      <c r="R14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B15">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C15">
+        <v>272.4895375</v>
+      </c>
+      <c r="D15">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E15">
+        <v>0.00992063492063492</v>
+      </c>
+      <c r="F15">
+        <v>87.41209930328283</v>
+      </c>
+      <c r="G15">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H15">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I15">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J15">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K15">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L15">
+        <v>4052.4</v>
+      </c>
+      <c r="M15">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N15">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O15">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P15">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>104</v>
+      </c>
+      <c r="R15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B16">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C16">
+        <v>294.2310833333333</v>
+      </c>
+      <c r="D16">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E16">
+        <v>0.4563492063492064</v>
+      </c>
+      <c r="F16">
+        <v>86.72860544276536</v>
+      </c>
+      <c r="G16">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H16">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I16">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J16">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K16">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L16">
+        <v>4052.4</v>
+      </c>
+      <c r="M16">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N16">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O16">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P16">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>105</v>
+      </c>
+      <c r="R16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B17">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C17">
+        <v>296.4974166666667</v>
+      </c>
+      <c r="D17">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>87.98746317893055</v>
+      </c>
+      <c r="G17">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H17">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I17">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J17">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K17">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L17">
+        <v>4052.4</v>
+      </c>
+      <c r="M17">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N17">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O17">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P17">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>106</v>
+      </c>
+      <c r="R17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B18">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C18">
+        <v>301.4811708333334</v>
+      </c>
+      <c r="D18">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>87.68326523544027</v>
+      </c>
+      <c r="G18">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H18">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I18">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J18">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K18">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L18">
+        <v>4052.4</v>
+      </c>
+      <c r="M18">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N18">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O18">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P18">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>107</v>
+      </c>
+      <c r="R18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="A19">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B19">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C19">
+        <v>299.770525</v>
+      </c>
+      <c r="D19">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>88.25994783771715</v>
+      </c>
+      <c r="G19">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H19">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I19">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J19">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K19">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L19">
+        <v>4052.4</v>
+      </c>
+      <c r="M19">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N19">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O19">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P19">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>108</v>
+      </c>
+      <c r="R19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="A20">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B20">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C20">
+        <v>312.9457666666667</v>
+      </c>
+      <c r="D20">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>87.74750409970341</v>
+      </c>
+      <c r="G20">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H20">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I20">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J20">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K20">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L20">
+        <v>4052.4</v>
+      </c>
+      <c r="M20">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N20">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O20">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P20">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>109</v>
+      </c>
+      <c r="R20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B21">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C21">
+        <v>324.9791250000001</v>
+      </c>
+      <c r="D21">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>87.29663474662485</v>
+      </c>
+      <c r="G21">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H21">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I21">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J21">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K21">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L21">
+        <v>4052.4</v>
+      </c>
+      <c r="M21">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N21">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O21">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P21">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>110</v>
+      </c>
+      <c r="R21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B22">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C22">
+        <v>318.8883541666667</v>
+      </c>
+      <c r="D22">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E22">
+        <v>0.2281746031746032</v>
+      </c>
+      <c r="F22">
+        <v>86.37631125186759</v>
+      </c>
+      <c r="G22">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H22">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I22">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J22">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K22">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L22">
+        <v>4052.4</v>
+      </c>
+      <c r="M22">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N22">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O22">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P22">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>111</v>
+      </c>
+      <c r="R22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B23">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C23">
+        <v>359.1985791666667</v>
+      </c>
+      <c r="D23">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E23">
+        <v>0.6845238095238095</v>
+      </c>
+      <c r="F23">
+        <v>86.21083398410664</v>
+      </c>
+      <c r="G23">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H23">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I23">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J23">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K23">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L23">
+        <v>4052.4</v>
+      </c>
+      <c r="M23">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N23">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O23">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P23">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>112</v>
+      </c>
+      <c r="R23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="A24">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B24">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C24">
+        <v>360.3034166666667</v>
+      </c>
+      <c r="D24">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E24">
+        <v>0.4365079365079365</v>
+      </c>
+      <c r="F24">
+        <v>86.38055353011005</v>
+      </c>
+      <c r="G24">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H24">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I24">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J24">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K24">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L24">
+        <v>4052.4</v>
+      </c>
+      <c r="M24">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N24">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O24">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P24">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>113</v>
+      </c>
+      <c r="R24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="A25">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B25">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C25">
+        <v>364.8404416666666</v>
+      </c>
+      <c r="D25">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E25">
+        <v>0.3075396825396826</v>
+      </c>
+      <c r="F25">
+        <v>85.09650189143508</v>
+      </c>
+      <c r="G25">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H25">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I25">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J25">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K25">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L25">
+        <v>4052.4</v>
+      </c>
+      <c r="M25">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N25">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O25">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P25">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>114</v>
+      </c>
+      <c r="R25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="A26">
+        <v>2490.979048693252</v>
+      </c>
+      <c r="B26">
+        <v>29.02095130674866</v>
+      </c>
+      <c r="C26">
+        <v>375.5902708333333</v>
+      </c>
+      <c r="D26">
+        <v>0.01151625051855105</v>
+      </c>
+      <c r="E26">
+        <v>3.412698412698413</v>
+      </c>
+      <c r="F26">
+        <v>83.83662609026656</v>
+      </c>
+      <c r="G26">
+        <v>233.653872100766</v>
+      </c>
+      <c r="H26">
+        <v>16036.34612789925</v>
+      </c>
+      <c r="I26">
+        <v>0.01436102471424497</v>
+      </c>
+      <c r="J26">
+        <v>0.5360786724031961</v>
+      </c>
+      <c r="K26">
+        <v>53.74778871280043</v>
+      </c>
+      <c r="L26">
+        <v>4052.4</v>
+      </c>
+      <c r="M26">
+        <v>1.326319926779203</v>
+      </c>
+      <c r="N26">
+        <v>1.436102471424497</v>
+      </c>
+      <c r="O26">
+        <v>98.56389752857551</v>
+      </c>
+      <c r="P26">
+        <v>3998.652211287199</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>115</v>
+      </c>
+      <c r="R26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>